--- a/public/res/leaderboards/Beginner.xlsx
+++ b/public/res/leaderboards/Beginner.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lawrence\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF131441-8E8D-4522-A333-F194EA9B8722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AF2FE3-8AF3-43CF-9DF7-9AA2F60A5400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{390FB6FF-58F2-4FE8-ABCA-50770D81142D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>#</t>
   </si>
@@ -125,9 +125,6 @@
     <t>Rui Ke Yap</t>
   </si>
   <si>
-    <t xml:space="preserve">Jordan Rao </t>
-  </si>
-  <si>
     <t xml:space="preserve">Daniel  Thenamkodath </t>
   </si>
   <si>
@@ -143,9 +140,6 @@
     <t>Natalie Gu</t>
   </si>
   <si>
-    <t>Kyle  Stutz</t>
-  </si>
-  <si>
     <t>Lachlan Wu</t>
   </si>
   <si>
@@ -218,9 +212,6 @@
     <t>Santiago Rodriguez</t>
   </si>
   <si>
-    <t>Gary Chen</t>
-  </si>
-  <si>
     <t>Bofan Zhao</t>
   </si>
   <si>
@@ -237,6 +228,69 @@
   </si>
   <si>
     <t>sonaa aneja</t>
+  </si>
+  <si>
+    <t>benjamin allsop</t>
+  </si>
+  <si>
+    <t>Warren Kusuma</t>
+  </si>
+  <si>
+    <t>Zachary Tan</t>
+  </si>
+  <si>
+    <t>Yanni Karlaftis</t>
+  </si>
+  <si>
+    <t>Owen Ciantar</t>
+  </si>
+  <si>
+    <t>Kanha Mittal</t>
+  </si>
+  <si>
+    <t>Hao Zhang</t>
+  </si>
+  <si>
+    <t>Kristy Wong</t>
+  </si>
+  <si>
+    <t>Emma Nguyen</t>
+  </si>
+  <si>
+    <t>caitlyn gorry</t>
+  </si>
+  <si>
+    <t>Michael Duong</t>
+  </si>
+  <si>
+    <t>Aydin Evans</t>
+  </si>
+  <si>
+    <t>Itsuki Cheng</t>
+  </si>
+  <si>
+    <t>Kyle Stutz</t>
+  </si>
+  <si>
+    <t>Akshat</t>
+  </si>
+  <si>
+    <t>Yinghua Fu</t>
+  </si>
+  <si>
+    <t>Aditeya Purbey</t>
+  </si>
+  <si>
+    <t>amelia chang</t>
+  </si>
+  <si>
+    <t>vy phan</t>
+  </si>
+  <si>
+    <t>kuiyuan</t>
+  </si>
+  <si>
+    <t>Danny Lee</t>
   </si>
 </sst>
 </file>
@@ -637,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41A96F1F-0F5E-43CE-BA7C-B43E35F4018A}">
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
@@ -677,13 +731,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C2">
-        <v>134800</v>
+        <v>76900</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>131400</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -698,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>134800</v>
+        <v>208300</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -706,13 +760,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>121300</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>178200</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -727,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>121300</v>
+        <v>178200</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -735,13 +789,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C4">
-        <v>103700</v>
+        <v>67000</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>85300</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -756,7 +810,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>103700</v>
+        <v>152300</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -764,13 +818,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C5">
-        <v>78400</v>
+        <v>34200</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>107300</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -785,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>78400</v>
+        <v>141500</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -793,13 +847,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C6">
-        <v>78100</v>
+        <v>21900</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>114800</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -814,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>78100</v>
+        <v>136700</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -822,13 +876,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>76900</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
+        <v>134800</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -843,7 +894,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>76900</v>
+        <v>134800</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -851,13 +902,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>76800</v>
+        <v>103700</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>26100</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -872,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>76800</v>
+        <v>129800</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -880,13 +931,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>76600</v>
+        <v>121300</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -901,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>76600</v>
+        <v>123300</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -909,13 +960,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C10">
-        <v>68000</v>
+        <v>43500</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>58600</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -930,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>68000</v>
+        <v>102100</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -938,13 +989,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="C11">
-        <v>67000</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>95600</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -959,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>67000</v>
+        <v>95600</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -967,13 +1018,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="C12">
-        <v>66900</v>
+        <v>17300</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>88200</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -988,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>66900</v>
+        <v>90500</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -996,13 +1047,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C13">
-        <v>66500</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1017,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>66500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -1025,13 +1076,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>66400</v>
+        <v>76800</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>4900</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1046,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>66400</v>
+        <v>81700</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -1054,13 +1105,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15">
-        <v>62300</v>
+        <v>66400</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1075,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>62300</v>
+        <v>79400</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -1083,10 +1134,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C16">
-        <v>55700</v>
+        <v>78400</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1104,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>55700</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1112,10 +1163,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C17">
-        <v>53800</v>
+        <v>78100</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -1133,7 +1184,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>53800</v>
+        <v>78100</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -1141,10 +1192,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C18">
-        <v>51100</v>
+        <v>76600</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -1162,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>51100</v>
+        <v>76600</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -1170,10 +1221,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C19">
-        <v>49400</v>
+        <v>68000</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -1191,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>49400</v>
+        <v>68000</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -1199,13 +1250,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C20">
-        <v>46900</v>
+        <v>25200</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1220,7 +1271,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>46900</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -1228,10 +1279,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C21">
-        <v>45900</v>
+        <v>66900</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -1249,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>45900</v>
+        <v>66900</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -1257,10 +1308,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C22">
-        <v>43500</v>
+        <v>66500</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -1278,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>43500</v>
+        <v>66500</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -1286,13 +1337,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C23">
-        <v>37600</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>64200</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1307,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>37600</v>
+        <v>64200</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1315,10 +1366,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C24">
-        <v>36300</v>
+        <v>62300</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1336,7 +1387,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>36300</v>
+        <v>62300</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1344,13 +1395,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="C25">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1365,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>35000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1373,13 +1424,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="C26">
-        <v>34500</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>57900</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1394,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>34500</v>
+        <v>57900</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1402,13 +1453,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C27">
-        <v>34300</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>57600</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1423,7 +1474,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>34300</v>
+        <v>57600</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -1431,13 +1482,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C28">
-        <v>34200</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1452,7 +1503,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>34200</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -1460,10 +1511,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C29">
-        <v>32900</v>
+        <v>55700</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1481,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>32900</v>
+        <v>55700</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -1489,13 +1540,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="C30">
-        <v>31800</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>54200</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1510,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>31800</v>
+        <v>54200</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -1518,10 +1569,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C31">
-        <v>31600</v>
+        <v>53800</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -1539,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>31600</v>
+        <v>53800</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -1550,10 +1601,10 @@
         <v>39</v>
       </c>
       <c r="C32">
-        <v>31400</v>
+        <v>28500</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1568,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>31400</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
@@ -1576,10 +1627,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C33">
-        <v>30500</v>
+        <v>51100</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -1597,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>30500</v>
+        <v>51100</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
@@ -1605,13 +1656,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C34">
-        <v>28500</v>
+        <v>31800</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>19200</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1626,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>28500</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
@@ -1634,10 +1685,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C35">
-        <v>27400</v>
+        <v>49400</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -1655,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>27400</v>
+        <v>49400</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
@@ -1663,13 +1714,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="C36">
-        <v>27400</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>49300</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1684,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>27400</v>
+        <v>49300</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
@@ -1692,13 +1743,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C37">
-        <v>26200</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>48700</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1713,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>26200</v>
+        <v>48700</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -1721,10 +1772,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C38">
-        <v>25200</v>
+        <v>46900</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -1742,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>25200</v>
+        <v>46900</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
@@ -1750,13 +1801,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C39">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>41800</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1771,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>25000</v>
+        <v>41800</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
@@ -1779,13 +1830,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C40">
-        <v>25000</v>
+        <v>12400</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>29400</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1800,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>25000</v>
+        <v>41800</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
@@ -1808,13 +1859,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C41">
-        <v>23000</v>
+        <v>17100</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1829,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>23000</v>
+        <v>40100</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
@@ -1837,13 +1888,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C42">
-        <v>22800</v>
+        <v>16500</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1858,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>22800</v>
+        <v>39500</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -1866,10 +1917,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C43">
-        <v>22600</v>
+        <v>36300</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -1887,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>22600</v>
+        <v>36300</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
@@ -1895,10 +1946,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C44">
-        <v>22500</v>
+        <v>34500</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -1916,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>22500</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
@@ -1924,10 +1975,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C45">
-        <v>21900</v>
+        <v>34300</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -1945,7 +1996,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>21900</v>
+        <v>34300</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
@@ -1953,13 +2004,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C46">
-        <v>18100</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>33500</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1974,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>18100</v>
+        <v>33500</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
@@ -1982,10 +2033,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C47">
-        <v>17700</v>
+        <v>31600</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2003,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>17700</v>
+        <v>31600</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
@@ -2011,10 +2062,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="C48">
-        <v>17300</v>
+        <v>31400</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2032,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>17300</v>
+        <v>31400</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
@@ -2040,10 +2091,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C49">
-        <v>17100</v>
+        <v>30500</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2061,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>17100</v>
+        <v>30500</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
@@ -2069,10 +2120,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C50">
-        <v>17100</v>
+        <v>27400</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2090,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>17100</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
@@ -2098,10 +2149,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="C51">
-        <v>16500</v>
+        <v>27400</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2119,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>16500</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
@@ -2127,13 +2178,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C52">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>26400</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2148,7 +2199,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>10000</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
@@ -2156,10 +2207,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C53">
-        <v>9400</v>
+        <v>26200</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2177,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>9400</v>
+        <v>26200</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
@@ -2185,10 +2236,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C54">
-        <v>7400</v>
+        <v>25000</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2206,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>7400</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
@@ -2214,10 +2265,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C55">
-        <v>5700</v>
+        <v>25000</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2235,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>5700</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
@@ -2243,13 +2294,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C56">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2264,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>3900</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
@@ -2272,10 +2323,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C57">
-        <v>2700</v>
+        <v>23000</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -2293,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>2700</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
@@ -2301,27 +2352,549 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>47</v>
+      </c>
+      <c r="C58">
+        <v>22800</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>22800</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>48</v>
+      </c>
+      <c r="C59">
+        <v>22600</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>22600</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60">
+        <v>37600</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>22600</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>49</v>
+      </c>
+      <c r="C61">
+        <v>22500</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>22500</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62">
+        <v>35000</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>80</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>18900</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>18900</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>51</v>
+      </c>
+      <c r="C64">
+        <v>18100</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>34</v>
+      </c>
+      <c r="C65">
+        <v>32900</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>17900</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66">
         <v>65</v>
       </c>
-      <c r="C58">
+      <c r="B66" t="s">
+        <v>52</v>
+      </c>
+      <c r="C66">
+        <v>17700</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>17700</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>55</v>
+      </c>
+      <c r="C67">
+        <v>17100</v>
+      </c>
+      <c r="D67">
+        <v>15000</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>17100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>81</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>16900</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>16900</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>82</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>15000</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>83</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>11600</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>11600</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>61</v>
+      </c>
+      <c r="C71">
         <v>2700</v>
       </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
-      </c>
-      <c r="I58">
+      <c r="D71">
+        <v>7900</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>10600</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>57</v>
+      </c>
+      <c r="C72">
+        <v>9400</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>9400</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>58</v>
+      </c>
+      <c r="C73">
+        <v>7400</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74">
+        <v>5700</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>60</v>
+      </c>
+      <c r="C75">
+        <v>3900</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>62</v>
+      </c>
+      <c r="C76">
+        <v>2700</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
         <v>2700</v>
       </c>
     </row>

--- a/public/res/leaderboards/Beginner.xlsx
+++ b/public/res/leaderboards/Beginner.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lawrence\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AF2FE3-8AF3-43CF-9DF7-9AA2F60A5400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095389C0-A393-4ED2-B1EF-AD54F8FBD9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{390FB6FF-58F2-4FE8-ABCA-50770D81142D}"/>
+    <workbookView xWindow="8030" yWindow="2250" windowWidth="28800" windowHeight="15380" xr2:uid="{390FB6FF-58F2-4FE8-ABCA-50770D81142D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>#</t>
   </si>
@@ -215,12 +215,6 @@
     <t>Bofan Zhao</t>
   </si>
   <si>
-    <t>Nic Fiumara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jyothsna  Tummala </t>
-  </si>
-  <si>
     <t>Robyn Dunn</t>
   </si>
   <si>
@@ -257,9 +251,6 @@
     <t>Emma Nguyen</t>
   </si>
   <si>
-    <t>caitlyn gorry</t>
-  </si>
-  <si>
     <t>Michael Duong</t>
   </si>
   <si>
@@ -291,6 +282,75 @@
   </si>
   <si>
     <t>Danny Lee</t>
+  </si>
+  <si>
+    <t>Gabriel Calupig</t>
+  </si>
+  <si>
+    <t>James Dillon</t>
+  </si>
+  <si>
+    <t>Preston Long</t>
+  </si>
+  <si>
+    <t>Riley Porter</t>
+  </si>
+  <si>
+    <t>caitlin gorry</t>
+  </si>
+  <si>
+    <t>Henric Edvardsson</t>
+  </si>
+  <si>
+    <t>Yufeng Li</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sudarshan  Lakshminarasimhan </t>
+  </si>
+  <si>
+    <t>New Player</t>
+  </si>
+  <si>
+    <t>Jacob Thomas</t>
+  </si>
+  <si>
+    <t>Jyothsna Tummala</t>
+  </si>
+  <si>
+    <t>Cato</t>
+  </si>
+  <si>
+    <t>Cato Hobsbawn</t>
+  </si>
+  <si>
+    <t>Yiting Long</t>
+  </si>
+  <si>
+    <t>Yang Wang</t>
+  </si>
+  <si>
+    <t>Santiago Sassman</t>
+  </si>
+  <si>
+    <t>Dulan Yasamama</t>
+  </si>
+  <si>
+    <t>Anne Chua</t>
+  </si>
+  <si>
+    <t>Shubham Gupta</t>
+  </si>
+  <si>
+    <t>Preetish Choudhary</t>
+  </si>
+  <si>
+    <t>Sambhav  Saxena</t>
+  </si>
+  <si>
+    <t>Minhi Ng</t>
+  </si>
+  <si>
+    <t>Nick Lin</t>
   </si>
 </sst>
 </file>
@@ -691,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41A96F1F-0F5E-43CE-BA7C-B43E35F4018A}">
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
@@ -731,16 +791,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="C2">
-        <v>76900</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>131400</v>
+        <v>90000</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>197300</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -752,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>208300</v>
+        <v>287300</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -760,16 +820,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>103700</v>
       </c>
       <c r="D3">
-        <v>178200</v>
+        <v>26100</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>115000</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -781,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>178200</v>
+        <v>244800</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -789,16 +849,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>67000</v>
-      </c>
-      <c r="D4">
-        <v>85300</v>
+        <v>134800</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -810,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>152300</v>
+        <v>221800</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -818,13 +875,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>34200</v>
+        <v>76900</v>
       </c>
       <c r="D5">
-        <v>107300</v>
+        <v>131400</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -839,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>141500</v>
+        <v>208300</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -847,16 +904,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>21900</v>
+        <v>121300</v>
       </c>
       <c r="D6">
-        <v>114800</v>
+        <v>17000</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>74000</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -868,7 +925,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>136700</v>
+        <v>197300</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -876,13 +933,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="C7">
-        <v>134800</v>
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>178200</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -894,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>134800</v>
+        <v>192200</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -902,16 +962,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C8">
-        <v>103700</v>
+        <v>34200</v>
       </c>
       <c r="D8">
-        <v>26100</v>
+        <v>107300</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>45600</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -923,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>129800</v>
+        <v>172100</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -931,16 +991,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="C9">
-        <v>121300</v>
+        <v>17300</v>
       </c>
       <c r="D9">
-        <v>17000</v>
+        <v>88200</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -952,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>123300</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -960,13 +1020,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C10">
-        <v>43500</v>
+        <v>67000</v>
       </c>
       <c r="D10">
-        <v>58600</v>
+        <v>85300</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -981,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>102100</v>
+        <v>152300</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -989,16 +1049,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>95600</v>
+        <v>56000</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>88200</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1010,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>95600</v>
+        <v>144200</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -1018,16 +1078,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>17300</v>
+        <v>76800</v>
       </c>
       <c r="D12">
-        <v>88200</v>
+        <v>4900</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>73900</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1039,7 +1099,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>90500</v>
+        <v>140600</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -1047,16 +1107,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>76600</v>
       </c>
       <c r="D13">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>63700</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1068,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>90000</v>
+        <v>140300</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -1076,13 +1136,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C14">
-        <v>76800</v>
+        <v>21900</v>
       </c>
       <c r="D14">
-        <v>4900</v>
+        <v>114800</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1097,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>81700</v>
+        <v>136700</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -1105,16 +1165,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="C15">
-        <v>66400</v>
+        <v>17100</v>
       </c>
       <c r="D15">
-        <v>28000</v>
+        <v>15000</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>104400</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1126,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>79400</v>
+        <v>121500</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -1134,16 +1194,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C16">
-        <v>78400</v>
+        <v>28500</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>67800</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1155,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>78400</v>
+        <v>106300</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1163,16 +1223,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C17">
-        <v>78100</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>48700</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>56300</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1184,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>78100</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -1192,13 +1252,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C18">
-        <v>76600</v>
+        <v>43500</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>58600</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1213,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>76600</v>
+        <v>102100</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -1221,16 +1281,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="C19">
-        <v>68000</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>101000</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1242,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>68000</v>
+        <v>101000</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -1250,13 +1310,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="C20">
-        <v>25200</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>57000</v>
+        <v>99500</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1271,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>67200</v>
+        <v>99500</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -1279,16 +1339,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="C21">
-        <v>66900</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>57900</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>39400</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1300,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>66900</v>
+        <v>97300</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -1308,16 +1368,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C22">
-        <v>66500</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>95600</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1329,7 +1389,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>66500</v>
+        <v>96000</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -1337,16 +1397,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>64200</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1358,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>64200</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1366,16 +1426,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C24">
-        <v>62300</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>92900</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1387,7 +1447,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>62300</v>
+        <v>87900</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1395,16 +1455,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>62000</v>
+        <v>49300</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>37100</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1416,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>62000</v>
+        <v>86400</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1424,13 +1484,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>66400</v>
       </c>
       <c r="D26">
-        <v>57900</v>
+        <v>28000</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1445,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>57900</v>
+        <v>79400</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1453,16 +1513,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>57600</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>78600</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -1474,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>57600</v>
+        <v>78600</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -1482,13 +1542,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>78100</v>
       </c>
       <c r="D28">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1503,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>56000</v>
+        <v>78100</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -1511,16 +1571,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="C29">
-        <v>55700</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>77000</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -1532,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>55700</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -1540,16 +1600,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>36300</v>
       </c>
       <c r="D30">
-        <v>54200</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>37600</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1561,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>54200</v>
+        <v>73900</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -1569,16 +1629,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C31">
-        <v>53800</v>
+        <v>49400</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="F31">
         <v>0</v>
@@ -1590,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>53800</v>
+        <v>73000</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -1598,16 +1658,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C32">
-        <v>28500</v>
+        <v>31800</v>
       </c>
       <c r="D32">
-        <v>25000</v>
+        <v>19200</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>20500</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1619,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>53500</v>
+        <v>71500</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
@@ -1627,16 +1687,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="C33">
-        <v>51100</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>68200</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1648,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>51100</v>
+        <v>68200</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
@@ -1656,13 +1716,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C34">
-        <v>31800</v>
+        <v>68000</v>
       </c>
       <c r="D34">
-        <v>19200</v>
+        <v>0</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1677,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>51000</v>
+        <v>68000</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
@@ -1685,16 +1745,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C35">
-        <v>49400</v>
+        <v>25200</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1706,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>49400</v>
+        <v>67200</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
@@ -1714,16 +1774,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>49300</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1735,7 +1795,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>49300</v>
+        <v>67000</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
@@ -1743,13 +1803,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>66900</v>
       </c>
       <c r="D37">
-        <v>48700</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1764,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>48700</v>
+        <v>66900</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -1772,10 +1832,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C38">
-        <v>46900</v>
+        <v>66500</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -1793,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>46900</v>
+        <v>66500</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
@@ -1801,13 +1861,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>41800</v>
+        <v>64200</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1822,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>41800</v>
+        <v>64200</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
@@ -1830,13 +1890,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="C40">
-        <v>12400</v>
+        <v>78400</v>
       </c>
       <c r="D40">
-        <v>29400</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1851,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>41800</v>
+        <v>63400</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
@@ -1859,13 +1919,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C41">
-        <v>17100</v>
+        <v>62300</v>
       </c>
       <c r="D41">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1880,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>40100</v>
+        <v>62300</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
@@ -1888,16 +1948,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="C42">
-        <v>16500</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>61000</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1909,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>39500</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -1917,16 +1977,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="C43">
-        <v>36300</v>
+        <v>5700</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>28600</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>41500</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1938,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>36300</v>
+        <v>60800</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
@@ -1946,13 +2006,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="C44">
-        <v>34500</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>54200</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1967,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>34500</v>
+        <v>54200</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
@@ -1975,10 +2035,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="C45">
-        <v>34300</v>
+        <v>53800</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -1996,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>34300</v>
+        <v>53800</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
@@ -2004,13 +2064,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>33500</v>
+        <v>62000</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2025,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>33500</v>
+        <v>47000</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
@@ -2033,10 +2093,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C47">
-        <v>31600</v>
+        <v>46900</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2054,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>31600</v>
+        <v>46900</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
@@ -2062,16 +2122,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C48">
-        <v>31400</v>
+        <v>2700</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>35700</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2083,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>31400</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
@@ -2091,16 +2151,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="C49">
-        <v>30500</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>43200</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2112,7 +2172,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>30500</v>
+        <v>43200</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
@@ -2120,16 +2180,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="C50">
-        <v>27400</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>43200</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2141,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>27400</v>
+        <v>43200</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
@@ -2149,13 +2209,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C51">
-        <v>27400</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>57600</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2170,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>27400</v>
+        <v>42600</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
@@ -2178,13 +2238,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>26400</v>
+        <v>41800</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2199,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>26400</v>
+        <v>41800</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
@@ -2207,13 +2267,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C53">
-        <v>26200</v>
+        <v>12400</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>29400</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2228,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>26200</v>
+        <v>41800</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
@@ -2236,10 +2296,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C54">
-        <v>25000</v>
+        <v>55700</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2257,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>25000</v>
+        <v>40700</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
@@ -2265,13 +2325,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C55">
-        <v>25000</v>
+        <v>16500</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2286,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>25000</v>
+        <v>39500</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
@@ -2294,13 +2354,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>51100</v>
       </c>
       <c r="D56">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2315,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>25000</v>
+        <v>36100</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
@@ -2323,16 +2383,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="C57">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>34800</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2344,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>23000</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
@@ -2352,16 +2412,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="C58">
-        <v>22800</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>34500</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2373,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>22800</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
@@ -2381,10 +2441,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C59">
-        <v>22600</v>
+        <v>34500</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -2402,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>22600</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
@@ -2410,10 +2470,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="C60">
-        <v>37600</v>
+        <v>34400</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -2431,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>22600</v>
+        <v>34400</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
@@ -2439,10 +2499,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C61">
-        <v>22500</v>
+        <v>34300</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -2460,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>22500</v>
+        <v>34300</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
@@ -2468,13 +2528,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="C62">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>48400</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -2489,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>20000</v>
+        <v>33400</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
@@ -2497,13 +2557,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>18900</v>
+        <v>33300</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2518,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>18900</v>
+        <v>33300</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
@@ -2526,13 +2586,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="C64">
-        <v>18100</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>47500</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2547,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>18100</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
@@ -2555,10 +2615,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C65">
-        <v>32900</v>
+        <v>31600</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2576,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>17900</v>
+        <v>31600</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
@@ -2584,10 +2644,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C66">
-        <v>17700</v>
+        <v>31400</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2605,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>17700</v>
+        <v>31400</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
@@ -2613,13 +2673,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="C67">
-        <v>17100</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>15000</v>
+        <v>45200</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2634,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>17100</v>
+        <v>30200</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
@@ -2642,13 +2702,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>27400</v>
       </c>
       <c r="D68">
-        <v>16900</v>
+        <v>0</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2663,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>16900</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
@@ -2671,13 +2731,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>27400</v>
       </c>
       <c r="D69">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2692,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>15000</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
@@ -2700,13 +2760,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>11600</v>
+        <v>26400</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2721,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>11600</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
@@ -2729,13 +2789,13 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C71">
-        <v>2700</v>
+        <v>26200</v>
       </c>
       <c r="D71">
-        <v>7900</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2750,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>10600</v>
+        <v>26200</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
@@ -2758,16 +2818,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="C72">
-        <v>9400</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -2779,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>9400</v>
+        <v>26000</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
@@ -2787,13 +2847,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C73">
-        <v>7400</v>
+        <v>17100</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2808,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>7400</v>
+        <v>25100</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
@@ -2816,10 +2876,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C74">
-        <v>5700</v>
+        <v>25000</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2837,7 +2897,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>5700</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
@@ -2845,10 +2905,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C75">
-        <v>3900</v>
+        <v>25000</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2866,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>3900</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
@@ -2874,27 +2934,607 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>25000</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77">
+        <v>23000</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>47</v>
+      </c>
+      <c r="C78">
+        <v>22800</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>22800</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>48</v>
+      </c>
+      <c r="C79">
+        <v>22600</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>22600</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80">
+        <v>37600</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>22600</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81">
+        <v>35000</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>102</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>18600</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>18600</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>74</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>33500</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>51</v>
+      </c>
+      <c r="C84">
+        <v>18100</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>52</v>
+      </c>
+      <c r="C85">
+        <v>17700</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>17700</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>78</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>16900</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>16900</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>38</v>
+      </c>
+      <c r="C87">
+        <v>30500</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>15000</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>103</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>15000</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>80</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>11600</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>11600</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>57</v>
+      </c>
+      <c r="C91">
+        <v>9400</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>9400</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>49</v>
+      </c>
+      <c r="C92">
+        <v>22500</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>58</v>
+      </c>
+      <c r="C93">
+        <v>3900</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>77</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
+        <v>18900</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>34</v>
+      </c>
+      <c r="C95">
+        <v>32900</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>60</v>
+      </c>
+      <c r="C96">
         <v>2700</v>
       </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-      <c r="F76">
-        <v>0</v>
-      </c>
-      <c r="G76">
-        <v>0</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76">
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
         <v>2700</v>
       </c>
     </row>

--- a/public/res/leaderboards/Beginner.xlsx
+++ b/public/res/leaderboards/Beginner.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lawrence\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095389C0-A393-4ED2-B1EF-AD54F8FBD9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2D7D36-58DA-430F-9556-ED00A35F99B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8030" yWindow="2250" windowWidth="28800" windowHeight="15380" xr2:uid="{390FB6FF-58F2-4FE8-ABCA-50770D81142D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{390FB6FF-58F2-4FE8-ABCA-50770D81142D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
   <si>
     <t>#</t>
   </si>
@@ -143,9 +143,6 @@
     <t>Lachlan Wu</t>
   </si>
   <si>
-    <t>Jacob Senior</t>
-  </si>
-  <si>
     <t>Amita Lin</t>
   </si>
   <si>
@@ -233,9 +230,6 @@
     <t>Zachary Tan</t>
   </si>
   <si>
-    <t>Yanni Karlaftis</t>
-  </si>
-  <si>
     <t>Owen Ciantar</t>
   </si>
   <si>
@@ -308,9 +302,6 @@
     <t xml:space="preserve">Sudarshan  Lakshminarasimhan </t>
   </si>
   <si>
-    <t>New Player</t>
-  </si>
-  <si>
     <t>Jacob Thomas</t>
   </si>
   <si>
@@ -329,9 +320,6 @@
     <t>Yang Wang</t>
   </si>
   <si>
-    <t>Santiago Sassman</t>
-  </si>
-  <si>
     <t>Dulan Yasamama</t>
   </si>
   <si>
@@ -351,6 +339,51 @@
   </si>
   <si>
     <t>Nick Lin</t>
+  </si>
+  <si>
+    <t>Parsa Babadi Noroozi</t>
+  </si>
+  <si>
+    <t>Arthur Zhao</t>
+  </si>
+  <si>
+    <t>Pranav Bhimani</t>
+  </si>
+  <si>
+    <t>Abhiram S</t>
+  </si>
+  <si>
+    <t>Yianni Romanidis</t>
+  </si>
+  <si>
+    <t>Daniel Wong</t>
+  </si>
+  <si>
+    <t>Chris Chau</t>
+  </si>
+  <si>
+    <t>Zi Yang</t>
+  </si>
+  <si>
+    <t>Andrew Faser</t>
+  </si>
+  <si>
+    <t>Pranay Sorathia</t>
+  </si>
+  <si>
+    <t>Adam Healey</t>
+  </si>
+  <si>
+    <t>Sean Chan</t>
+  </si>
+  <si>
+    <t>My Nguyen</t>
+  </si>
+  <si>
+    <t>Navya Petet</t>
+  </si>
+  <si>
+    <t>Nic Fiumara</t>
   </si>
 </sst>
 </file>
@@ -751,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41A96F1F-0F5E-43CE-BA7C-B43E35F4018A}">
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
@@ -791,19 +824,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>134800</v>
       </c>
       <c r="D2">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>197300</v>
+        <v>87000</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>129400</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -812,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>287300</v>
+        <v>351200</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -820,16 +853,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="C3">
-        <v>103700</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>26100</v>
+        <v>90000</v>
       </c>
       <c r="E3">
-        <v>115000</v>
+        <v>197300</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -841,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>244800</v>
+        <v>272300</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -849,16 +882,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>134800</v>
+        <v>103700</v>
+      </c>
+      <c r="D4">
+        <v>26100</v>
       </c>
       <c r="E4">
-        <v>87000</v>
+        <v>115000</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>32700</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -867,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>221800</v>
+        <v>262500</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -875,19 +911,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>76900</v>
+        <v>121300</v>
       </c>
       <c r="D5">
-        <v>131400</v>
+        <v>17000</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>74000</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -896,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>208300</v>
+        <v>212300</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -904,16 +940,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>121300</v>
+        <v>76900</v>
       </c>
       <c r="D6">
-        <v>17000</v>
+        <v>131400</v>
       </c>
       <c r="E6">
-        <v>74000</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -925,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>197300</v>
+        <v>208300</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -933,19 +969,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>178200</v>
+        <v>10000</v>
       </c>
       <c r="E7">
-        <v>14000</v>
+        <v>92900</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>114500</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -954,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>192200</v>
+        <v>202400</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -962,16 +998,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C8">
-        <v>34200</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>107300</v>
+        <v>178200</v>
       </c>
       <c r="E8">
-        <v>45600</v>
+        <v>14000</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -983,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>172100</v>
+        <v>192200</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -991,19 +1027,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C9">
-        <v>17300</v>
+        <v>28500</v>
       </c>
       <c r="D9">
-        <v>88200</v>
+        <v>25000</v>
       </c>
       <c r="E9">
-        <v>67000</v>
+        <v>67800</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100300</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1012,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>157500</v>
+        <v>191600</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -1020,19 +1056,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="C10">
-        <v>67000</v>
+        <v>5700</v>
       </c>
       <c r="D10">
-        <v>85300</v>
+        <v>28600</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>41500</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>113100</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1041,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>152300</v>
+        <v>173900</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -1049,16 +1085,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>34200</v>
       </c>
       <c r="D11">
-        <v>56000</v>
+        <v>107300</v>
       </c>
       <c r="E11">
-        <v>88200</v>
+        <v>45600</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1070,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>144200</v>
+        <v>172100</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -1078,19 +1114,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="C12">
-        <v>76800</v>
+        <v>17100</v>
       </c>
       <c r="D12">
-        <v>4900</v>
+        <v>38000</v>
       </c>
       <c r="E12">
-        <v>73900</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>156700</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1099,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>140600</v>
+        <v>166800</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -1107,19 +1143,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C13">
-        <v>76600</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>49300</v>
       </c>
       <c r="E13">
-        <v>63700</v>
+        <v>37100</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>66600</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1128,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>140300</v>
+        <v>153000</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -1136,13 +1172,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="C14">
-        <v>21900</v>
+        <v>67000</v>
       </c>
       <c r="D14">
-        <v>114800</v>
+        <v>85300</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1157,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>136700</v>
+        <v>152300</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -1165,16 +1201,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C15">
-        <v>17100</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>15000</v>
+        <v>56000</v>
       </c>
       <c r="E15">
-        <v>104400</v>
+        <v>88200</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1186,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>121500</v>
+        <v>144200</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -1194,16 +1230,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C16">
-        <v>28500</v>
+        <v>17300</v>
       </c>
       <c r="D16">
-        <v>25000</v>
+        <v>88200</v>
       </c>
       <c r="E16">
-        <v>67800</v>
+        <v>67000</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1215,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>106300</v>
+        <v>142500</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1223,7 +1259,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1235,7 +1271,7 @@
         <v>56300</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>50700</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1244,7 +1280,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>105000</v>
+        <v>140700</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -1252,16 +1288,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C18">
-        <v>43500</v>
+        <v>76600</v>
       </c>
       <c r="D18">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>63700</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1273,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>102100</v>
+        <v>140300</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -1281,16 +1317,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>21900</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>114800</v>
       </c>
       <c r="E19">
-        <v>101000</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1302,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>101000</v>
+        <v>136700</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -1310,19 +1346,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>99500</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>76000</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>54700</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1331,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>99500</v>
+        <v>130700</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -1339,16 +1375,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>76800</v>
       </c>
       <c r="D21">
-        <v>57900</v>
+        <v>4900</v>
       </c>
       <c r="E21">
-        <v>39400</v>
+        <v>73900</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1360,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>97300</v>
+        <v>125600</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -1368,16 +1404,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>17100</v>
       </c>
       <c r="D22">
-        <v>95600</v>
+        <v>15000</v>
       </c>
       <c r="E22">
-        <v>15400</v>
+        <v>104400</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1389,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>96000</v>
+        <v>121500</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -1397,7 +1433,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1406,10 +1442,10 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>118800</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1418,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>90000</v>
+        <v>118800</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1432,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>92900</v>
+        <v>78600</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>51500</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1447,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>87900</v>
+        <v>115100</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1455,19 +1491,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>49300</v>
+        <v>47500</v>
       </c>
       <c r="E25">
-        <v>37100</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>78600</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1476,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>86400</v>
+        <v>111100</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1484,19 +1520,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="C26">
-        <v>66400</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>59000</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>49100</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1505,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>79400</v>
+        <v>108100</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1513,7 +1549,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1522,10 +1558,10 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>78600</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>102900</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1534,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>78600</v>
+        <v>102900</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -1542,13 +1578,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C28">
-        <v>78100</v>
+        <v>43500</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>58600</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1563,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>78100</v>
+        <v>102100</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -1571,19 +1607,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>64200</v>
       </c>
       <c r="E29">
-        <v>77000</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>35700</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1592,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>77000</v>
+        <v>99900</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -1600,16 +1636,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="C30">
-        <v>36300</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>99500</v>
       </c>
       <c r="E30">
-        <v>37600</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -1621,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>73900</v>
+        <v>99500</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -1629,19 +1665,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="C31">
-        <v>49400</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>23600</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>98000</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -1650,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>73000</v>
+        <v>98000</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -1658,16 +1694,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="C32">
-        <v>31800</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>19200</v>
+        <v>57900</v>
       </c>
       <c r="E32">
-        <v>20500</v>
+        <v>39400</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1679,7 +1715,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>71500</v>
+        <v>97300</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
@@ -1687,7 +1723,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -1696,10 +1732,10 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>68200</v>
+        <v>77000</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>18300</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -1708,7 +1744,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>68200</v>
+        <v>95300</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
@@ -1716,19 +1752,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="C34">
-        <v>68000</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>33500</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -1737,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>68000</v>
+        <v>90500</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
@@ -1745,16 +1781,16 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="C35">
-        <v>25200</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>15000</v>
+        <v>90000</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -1766,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>67200</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
@@ -1774,7 +1810,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -1783,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>67000</v>
+        <v>101000</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1795,7 +1831,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>67000</v>
+        <v>86000</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
@@ -1803,16 +1839,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="C37">
-        <v>66900</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>95600</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -1824,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>66900</v>
+        <v>81000</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -1832,13 +1868,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C38">
-        <v>66500</v>
+        <v>66400</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1853,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>66500</v>
+        <v>79400</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
@@ -1861,19 +1897,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>22500</v>
       </c>
       <c r="D39">
-        <v>64200</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>86300</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -1882,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>64200</v>
+        <v>78800</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
@@ -1890,19 +1926,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C40">
-        <v>78400</v>
+        <v>31800</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>19200</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>20500</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -1911,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>63400</v>
+        <v>78500</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
@@ -1919,10 +1955,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C41">
-        <v>62300</v>
+        <v>78100</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -1940,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>62300</v>
+        <v>78100</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
@@ -1948,16 +1984,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>36300</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>61000</v>
+        <v>37600</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1969,7 +2005,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>61000</v>
+        <v>73900</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -1977,19 +2013,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="C43">
-        <v>5700</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>28600</v>
+        <v>57600</v>
       </c>
       <c r="E43">
-        <v>41500</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>30500</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -1998,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>60800</v>
+        <v>73100</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
@@ -2006,16 +2042,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>49400</v>
       </c>
       <c r="D44">
-        <v>54200</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2027,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>54200</v>
+        <v>73000</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
@@ -2035,10 +2071,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C45">
-        <v>53800</v>
+        <v>68000</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -2056,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>53800</v>
+        <v>68000</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
@@ -2064,19 +2100,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>62000</v>
+        <v>0</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>67400</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -2085,7 +2121,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>47000</v>
+        <v>67400</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
@@ -2093,10 +2129,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="C47">
-        <v>46900</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -2105,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>66700</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -2114,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>46900</v>
+        <v>66700</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
@@ -2122,16 +2158,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C48">
-        <v>2700</v>
+        <v>78400</v>
       </c>
       <c r="D48">
-        <v>7900</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>35700</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2143,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>46300</v>
+        <v>63400</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
@@ -2151,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>62300</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>43200</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2172,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>43200</v>
+        <v>62300</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
@@ -2180,7 +2216,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -2189,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>43200</v>
+        <v>61000</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2201,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>43200</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
@@ -2209,19 +2245,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>57600</v>
+        <v>0</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2230,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>42600</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
@@ -2238,13 +2274,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>41800</v>
+        <v>54200</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2259,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>41800</v>
+        <v>54200</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
@@ -2267,13 +2303,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C53">
-        <v>12400</v>
+        <v>53800</v>
       </c>
       <c r="D53">
-        <v>29400</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2288,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>41800</v>
+        <v>53800</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
@@ -2296,16 +2332,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="C54">
-        <v>55700</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>68200</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2317,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>40700</v>
+        <v>53200</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
@@ -2325,16 +2361,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C55">
-        <v>16500</v>
+        <v>25200</v>
       </c>
       <c r="D55">
-        <v>23000</v>
+        <v>57000</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2346,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>39500</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
@@ -2354,10 +2390,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C56">
-        <v>51100</v>
+        <v>66900</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2375,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>36100</v>
+        <v>51900</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
@@ -2383,16 +2419,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>66500</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>34800</v>
+        <v>0</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2404,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>34800</v>
+        <v>51500</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
@@ -2412,16 +2448,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>46900</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>34500</v>
+        <v>0</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2433,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>34500</v>
+        <v>46900</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
@@ -2441,16 +2477,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C59">
-        <v>34500</v>
+        <v>2700</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>35700</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -2462,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>34500</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
@@ -2470,19 +2506,19 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C60">
-        <v>34400</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>33300</v>
       </c>
       <c r="E60">
         <v>0</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -2491,7 +2527,7 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>34400</v>
+        <v>45300</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
@@ -2499,16 +2535,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C61">
-        <v>34300</v>
+        <v>0</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>43200</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -2520,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>34300</v>
+        <v>43200</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
@@ -2528,16 +2564,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>48400</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>43200</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -2549,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>33400</v>
+        <v>43200</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
@@ -2557,19 +2593,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>33300</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -2578,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>33300</v>
+        <v>43000</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
@@ -2586,13 +2622,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>47500</v>
+        <v>41800</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2607,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>32500</v>
+        <v>41800</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
@@ -2615,10 +2651,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C65">
-        <v>31600</v>
+        <v>55700</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2636,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>31600</v>
+        <v>40700</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
@@ -2644,13 +2680,13 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C66">
-        <v>31400</v>
+        <v>16500</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2665,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>31400</v>
+        <v>39500</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
@@ -2673,19 +2709,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>45200</v>
+        <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>34500</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -2694,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>30200</v>
+        <v>37800</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
@@ -2702,10 +2738,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C68">
-        <v>27400</v>
+        <v>51100</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -2723,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>27400</v>
+        <v>36100</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
@@ -2731,16 +2767,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="C69">
-        <v>27400</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>34800</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2752,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>27400</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
@@ -2760,13 +2796,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>34500</v>
       </c>
       <c r="D70">
-        <v>26400</v>
+        <v>0</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2781,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>26400</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
@@ -2789,10 +2825,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C71">
-        <v>26200</v>
+        <v>34300</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -2810,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>26200</v>
+        <v>34300</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
@@ -2818,19 +2854,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>37600</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
       <c r="E72">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>11200</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -2839,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>26000</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
@@ -2847,19 +2883,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="C73">
-        <v>17100</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>33400</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -2868,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>25100</v>
+        <v>33400</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
@@ -2876,13 +2912,13 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="C74">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>48400</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2897,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>25000</v>
+        <v>33400</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
@@ -2905,10 +2941,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="C75">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2917,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>32100</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -2926,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>25000</v>
+        <v>32100</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
@@ -2934,13 +2970,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>25000</v>
+        <v>62000</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2955,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>25000</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
@@ -2963,10 +2999,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C77">
-        <v>23000</v>
+        <v>31600</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2984,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>23000</v>
+        <v>31600</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
@@ -2992,10 +3028,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C78">
-        <v>22800</v>
+        <v>31400</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -3013,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>22800</v>
+        <v>31400</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
@@ -3021,10 +3057,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="C79">
-        <v>22600</v>
+        <v>0</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -3033,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>30800</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -3042,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>22600</v>
+        <v>30800</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
@@ -3050,10 +3086,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C80">
-        <v>37600</v>
+        <v>27400</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3071,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>22600</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
@@ -3079,10 +3115,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C81">
-        <v>35000</v>
+        <v>27400</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3100,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>20000</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
@@ -3108,16 +3144,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>12400</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>29400</v>
       </c>
       <c r="E82">
-        <v>18600</v>
+        <v>0</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -3129,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>18600</v>
+        <v>26800</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
@@ -3137,13 +3173,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>33500</v>
+        <v>26400</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3158,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>18500</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
@@ -3166,10 +3202,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C84">
-        <v>18100</v>
+        <v>26200</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3187,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="I84">
-        <v>18100</v>
+        <v>26200</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
@@ -3195,10 +3231,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="C85">
-        <v>17700</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -3207,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>25600</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -3216,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>17700</v>
+        <v>25600</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
@@ -3224,13 +3260,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="D86">
-        <v>16900</v>
+        <v>0</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3245,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>16900</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
@@ -3253,10 +3289,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C87">
-        <v>30500</v>
+        <v>25000</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3274,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>15500</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
@@ -3282,13 +3318,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3303,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>15000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
@@ -3311,16 +3347,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>103</v>
+        <v>45</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -3332,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="I89">
-        <v>15000</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
@@ -3340,13 +3376,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>22800</v>
       </c>
       <c r="D90">
-        <v>11600</v>
+        <v>0</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3361,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>11600</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
@@ -3369,10 +3405,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C91">
-        <v>9400</v>
+        <v>22600</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -3390,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>9400</v>
+        <v>22600</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
@@ -3398,10 +3434,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C92">
-        <v>22500</v>
+        <v>35000</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3419,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>7500</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
@@ -3427,16 +3463,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="C93">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>18600</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -3448,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="I93">
-        <v>3900</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
@@ -3456,13 +3492,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>18100</v>
       </c>
       <c r="D94">
-        <v>18900</v>
+        <v>0</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3477,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>3900</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
@@ -3485,10 +3521,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C95">
-        <v>32900</v>
+        <v>17700</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -3506,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="I95">
-        <v>2900</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
@@ -3514,28 +3550,347 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96">
+        <v>16900</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>16900</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>96</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <v>45200</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>15200</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>77</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98">
+        <v>15000</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>78</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <v>11600</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>11600</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>97</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>26000</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>113</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>9600</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>56</v>
+      </c>
+      <c r="C102">
+        <v>9400</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>9400</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>114</v>
+      </c>
+      <c r="C103">
+        <v>7400</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>13900</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>57</v>
+      </c>
+      <c r="C104">
+        <v>3900</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>75</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+      <c r="D105">
+        <v>18900</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>59</v>
+      </c>
+      <c r="C106">
         <v>2700</v>
       </c>
-      <c r="D96">
-        <v>0</v>
-      </c>
-      <c r="E96">
-        <v>0</v>
-      </c>
-      <c r="F96">
-        <v>0</v>
-      </c>
-      <c r="G96">
-        <v>0</v>
-      </c>
-      <c r="H96">
-        <v>0</v>
-      </c>
-      <c r="I96">
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
         <v>2700</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>37</v>
+      </c>
+      <c r="C107">
+        <v>30500</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/public/res/leaderboards/Beginner.xlsx
+++ b/public/res/leaderboards/Beginner.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lawrence\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2D7D36-58DA-430F-9556-ED00A35F99B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62E2750-11B8-4D49-8CF9-29BEC5E374AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{390FB6FF-58F2-4FE8-ABCA-50770D81142D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t>#</t>
   </si>
@@ -74,9 +74,6 @@
     <t>Qingzhe Sun</t>
   </si>
   <si>
-    <t>Ka Guan Neo</t>
-  </si>
-  <si>
     <t>Jacob Towns</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
     <t>Rui Ke Yap</t>
   </si>
   <si>
-    <t xml:space="preserve">Daniel  Thenamkodath </t>
-  </si>
-  <si>
     <t>Viet Thanh Nguyen</t>
   </si>
   <si>
@@ -191,9 +185,6 @@
     <t>Leonard Lee</t>
   </si>
   <si>
-    <t>Lakshay  Yadav</t>
-  </si>
-  <si>
     <t>Payan Kolah</t>
   </si>
   <si>
@@ -299,9 +290,6 @@
     <t>Yufeng Li</t>
   </si>
   <si>
-    <t xml:space="preserve">Sudarshan  Lakshminarasimhan </t>
-  </si>
-  <si>
     <t>Jacob Thomas</t>
   </si>
   <si>
@@ -332,9 +320,6 @@
     <t>Preetish Choudhary</t>
   </si>
   <si>
-    <t>Sambhav  Saxena</t>
-  </si>
-  <si>
     <t>Minhi Ng</t>
   </si>
   <si>
@@ -384,13 +369,31 @@
   </si>
   <si>
     <t>Nic Fiumara</t>
+  </si>
+  <si>
+    <t>Ka guan neo</t>
+  </si>
+  <si>
+    <t>Daniel Thenamkodath</t>
+  </si>
+  <si>
+    <t>gaurang dhir</t>
+  </si>
+  <si>
+    <t>Sudarshan Lakshminarasimhan</t>
+  </si>
+  <si>
+    <t>Lakshay Yadav</t>
+  </si>
+  <si>
+    <t>Sambhav Saxena</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -405,20 +408,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -441,15 +430,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -784,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41A96F1F-0F5E-43CE-BA7C-B43E35F4018A}">
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
@@ -794,28 +777,28 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -839,13 +822,13 @@
         <v>129400</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>132100</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>351200</v>
+        <v>483300</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -853,28 +836,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>103700</v>
       </c>
       <c r="D3">
-        <v>90000</v>
+        <v>26100</v>
       </c>
       <c r="E3">
-        <v>197300</v>
+        <v>115000</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32700</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>154800</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>272300</v>
+        <v>391200</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -882,28 +865,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C4">
-        <v>103700</v>
+        <v>34200</v>
       </c>
       <c r="D4">
-        <v>26100</v>
+        <v>107300</v>
       </c>
       <c r="E4">
-        <v>115000</v>
+        <v>45600</v>
       </c>
       <c r="F4">
-        <v>32700</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>194100</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>262500</v>
+        <v>366200</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -911,28 +894,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C5">
-        <v>121300</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>17000</v>
+        <v>48700</v>
       </c>
       <c r="E5">
-        <v>74000</v>
+        <v>56300</v>
       </c>
       <c r="F5">
-        <v>30000</v>
+        <v>50700</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>179200</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>212300</v>
+        <v>304900</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -940,7 +923,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>76900</v>
@@ -955,13 +938,13 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>54100</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>208300</v>
+        <v>262400</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -969,19 +952,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>10000</v>
+        <v>90000</v>
       </c>
       <c r="E7">
-        <v>92900</v>
+        <v>197300</v>
       </c>
       <c r="F7">
-        <v>114500</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -990,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>202400</v>
+        <v>257300</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -998,28 +981,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>28500</v>
       </c>
       <c r="D8">
-        <v>178200</v>
+        <v>25000</v>
       </c>
       <c r="E8">
-        <v>14000</v>
+        <v>67800</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>100300</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>87200</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>192200</v>
+        <v>253800</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -1027,28 +1010,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="C9">
-        <v>28500</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="E9">
-        <v>67800</v>
+        <v>92900</v>
       </c>
       <c r="F9">
-        <v>100300</v>
+        <v>114500</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>45200</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>191600</v>
+        <v>247600</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -1056,28 +1039,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C10">
-        <v>5700</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>28600</v>
+        <v>178200</v>
       </c>
       <c r="E10">
-        <v>41500</v>
+        <v>14000</v>
       </c>
       <c r="F10">
-        <v>113100</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>22600</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>173900</v>
+        <v>214800</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -1085,28 +1068,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="C11">
-        <v>34200</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>107300</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>45600</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>102900</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>111500</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>172100</v>
+        <v>214400</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -1114,19 +1097,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>17100</v>
+        <v>121300</v>
       </c>
       <c r="D12">
-        <v>38000</v>
+        <v>17000</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>74000</v>
       </c>
       <c r="F12">
-        <v>156700</v>
+        <v>30000</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1135,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>166800</v>
+        <v>212300</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -1143,28 +1126,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>17100</v>
       </c>
       <c r="D13">
-        <v>49300</v>
+        <v>15000</v>
       </c>
       <c r="E13">
-        <v>37100</v>
+        <v>104400</v>
       </c>
       <c r="F13">
-        <v>66600</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>88300</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>153000</v>
+        <v>209800</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
@@ -1172,28 +1155,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>67000</v>
+        <v>76600</v>
       </c>
       <c r="D14">
-        <v>85300</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>63700</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>59500</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>152300</v>
+        <v>184800</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
@@ -1201,28 +1184,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>22500</v>
       </c>
       <c r="D15">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>88200</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>86300</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>105000</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>144200</v>
+        <v>183800</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
@@ -1230,28 +1213,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>17300</v>
+        <v>76800</v>
       </c>
       <c r="D16">
-        <v>88200</v>
+        <v>4900</v>
       </c>
       <c r="E16">
-        <v>67000</v>
+        <v>73900</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>56300</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>142500</v>
+        <v>181900</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -1259,28 +1242,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="D17">
-        <v>48700</v>
+        <v>28600</v>
       </c>
       <c r="E17">
-        <v>56300</v>
+        <v>41500</v>
       </c>
       <c r="F17">
-        <v>50700</v>
+        <v>113100</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>140700</v>
+        <v>181700</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -1288,28 +1271,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="C18">
-        <v>76600</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>63700</v>
+        <v>15000</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>135000</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>140300</v>
+        <v>178000</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -1317,28 +1300,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>21900</v>
+        <v>49400</v>
       </c>
       <c r="D19">
-        <v>114800</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>23600</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>101700</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>136700</v>
+        <v>174700</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -1346,28 +1329,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>36300</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>76000</v>
+        <v>37600</v>
       </c>
       <c r="F20">
-        <v>54700</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>96000</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>130700</v>
+        <v>169900</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -1375,28 +1358,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="C21">
-        <v>76800</v>
+        <v>17300</v>
       </c>
       <c r="D21">
-        <v>4900</v>
+        <v>88200</v>
       </c>
       <c r="E21">
-        <v>73900</v>
+        <v>67000</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>25800</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>125600</v>
+        <v>153300</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -1404,19 +1387,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="C22">
-        <v>17100</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>15000</v>
+        <v>49300</v>
       </c>
       <c r="E22">
-        <v>104400</v>
+        <v>37100</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>66600</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1425,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>121500</v>
+        <v>153000</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -1433,19 +1416,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>85300</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>118800</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1454,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>118800</v>
+        <v>152300</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
@@ -1462,19 +1445,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>17100</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="E24">
-        <v>78600</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>51500</v>
+        <v>156700</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1483,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>115100</v>
+        <v>151800</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -1491,19 +1474,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>21900</v>
       </c>
       <c r="D25">
-        <v>47500</v>
+        <v>114800</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>78600</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1512,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>111100</v>
+        <v>136700</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -1520,28 +1503,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>37600</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>59000</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>49100</v>
+        <v>11200</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>97000</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>108100</v>
+        <v>130800</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
@@ -1549,19 +1532,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>88200</v>
       </c>
       <c r="F27">
-        <v>102900</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1570,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>102900</v>
+        <v>129200</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -1578,19 +1561,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="C28">
-        <v>43500</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>58600</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>118800</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -1599,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>102100</v>
+        <v>118800</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -1607,28 +1590,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>31800</v>
       </c>
       <c r="D29">
-        <v>64200</v>
+        <v>19200</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>20500</v>
       </c>
       <c r="F29">
-        <v>35700</v>
+        <v>7000</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>44900</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29">
-        <v>99900</v>
+        <v>116400</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
@@ -1636,19 +1619,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>99500</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>76000</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>54700</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -1657,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>99500</v>
+        <v>115700</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -1665,28 +1648,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>47500</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>98000</v>
+        <v>78600</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>98000</v>
+        <v>111100</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -1694,16 +1677,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>43500</v>
       </c>
       <c r="D32">
-        <v>57900</v>
+        <v>58600</v>
       </c>
       <c r="E32">
-        <v>39400</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1715,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>97300</v>
+        <v>102100</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
@@ -1723,7 +1706,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -1732,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>77000</v>
+        <v>78600</v>
       </c>
       <c r="F33">
-        <v>18300</v>
+        <v>51500</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -1744,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>95300</v>
+        <v>100100</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
@@ -1752,19 +1735,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>33500</v>
+        <v>99500</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -1773,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>90500</v>
+        <v>99500</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
@@ -1781,7 +1764,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -1790,10 +1773,10 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>98000</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -1802,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>90000</v>
+        <v>98000</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
@@ -1810,16 +1793,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>57900</v>
       </c>
       <c r="E36">
-        <v>101000</v>
+        <v>39400</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -1831,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>86000</v>
+        <v>97300</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
@@ -1839,19 +1822,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>95600</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>15400</v>
+        <v>77000</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>18300</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -1860,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>81000</v>
+        <v>95300</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -1868,13 +1851,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="C38">
-        <v>66400</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1883,13 +1866,13 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="H38">
         <v>0</v>
       </c>
       <c r="I38">
-        <v>79400</v>
+        <v>95000</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
@@ -1897,19 +1880,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="C39">
-        <v>22500</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>59000</v>
       </c>
       <c r="F39">
-        <v>86300</v>
+        <v>49100</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -1918,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>78800</v>
+        <v>93100</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
@@ -1926,19 +1909,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C40">
-        <v>31800</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>19200</v>
+        <v>33500</v>
       </c>
       <c r="E40">
-        <v>20500</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>7000</v>
+        <v>72000</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -1947,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>78500</v>
+        <v>90500</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
@@ -1955,16 +1938,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="C41">
-        <v>78100</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -1976,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>78100</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
@@ -1984,16 +1967,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="C42">
-        <v>36300</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>37600</v>
+        <v>101000</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2005,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>73900</v>
+        <v>86000</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -2013,19 +1996,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>57600</v>
+        <v>64200</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>30500</v>
+        <v>35700</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -2034,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>73100</v>
+        <v>84900</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
@@ -2042,28 +2025,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C44">
-        <v>49400</v>
+        <v>2700</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>7900</v>
       </c>
       <c r="E44">
-        <v>23600</v>
+        <v>35700</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>36800</v>
       </c>
       <c r="H44">
         <v>0</v>
       </c>
       <c r="I44">
-        <v>73000</v>
+        <v>83100</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
@@ -2071,13 +2054,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C45">
-        <v>68000</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2086,13 +2069,13 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>64400</v>
       </c>
       <c r="H45">
         <v>0</v>
       </c>
       <c r="I45">
-        <v>68000</v>
+        <v>81400</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
@@ -2100,10 +2083,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>12</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>78100</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -2112,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>67400</v>
+        <v>0</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -2121,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>67400</v>
+        <v>78100</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
@@ -2129,7 +2112,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -2141,16 +2124,16 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>66700</v>
+        <v>32100</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>58800</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
       <c r="I47">
-        <v>66700</v>
+        <v>75900</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
@@ -2158,28 +2141,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C48">
-        <v>78400</v>
+        <v>25200</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>22300</v>
       </c>
       <c r="H48">
         <v>0</v>
       </c>
       <c r="I48">
-        <v>63400</v>
+        <v>74500</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
@@ -2187,28 +2170,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="C49">
-        <v>62300</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>34500</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>35700</v>
       </c>
       <c r="H49">
         <v>0</v>
       </c>
       <c r="I49">
-        <v>62300</v>
+        <v>73500</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
@@ -2216,16 +2199,16 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>68000</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>61000</v>
+        <v>0</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2237,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>61000</v>
+        <v>68000</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
@@ -2245,7 +2228,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2257,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>57000</v>
+        <v>67400</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2266,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>57000</v>
+        <v>67400</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
@@ -2274,19 +2257,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>54200</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>0</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>66700</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -2295,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>54200</v>
+        <v>66700</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
@@ -2303,16 +2286,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="C53">
-        <v>53800</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>95600</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2324,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>53800</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
@@ -2332,16 +2315,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>66400</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="E54">
-        <v>68200</v>
+        <v>0</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2353,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>53200</v>
+        <v>64400</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
@@ -2361,16 +2344,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C55">
-        <v>25200</v>
+        <v>78400</v>
       </c>
       <c r="D55">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -2382,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>52200</v>
+        <v>63400</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
@@ -2390,10 +2373,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C56">
-        <v>66900</v>
+        <v>62300</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2411,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>51900</v>
+        <v>62300</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
@@ -2419,16 +2402,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="C57">
-        <v>66500</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>61000</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2440,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>51500</v>
+        <v>61000</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
@@ -2448,19 +2431,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="C58">
-        <v>46900</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>57600</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>30500</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -2469,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>46900</v>
+        <v>58100</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
@@ -2477,19 +2460,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="C59">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>7900</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>35700</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -2498,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>46300</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
@@ -2506,19 +2489,19 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>33300</v>
+        <v>54200</v>
       </c>
       <c r="E60">
         <v>0</v>
       </c>
       <c r="F60">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -2527,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>45300</v>
+        <v>54200</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
@@ -2535,16 +2518,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>53800</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>43200</v>
+        <v>0</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -2556,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>43200</v>
+        <v>53800</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
@@ -2564,16 +2547,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>66900</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>43200</v>
+        <v>0</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -2585,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>43200</v>
+        <v>51900</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
@@ -2593,19 +2576,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>66500</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -2614,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>43000</v>
+        <v>51500</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
@@ -2622,13 +2605,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>46900</v>
       </c>
       <c r="D64">
-        <v>41800</v>
+        <v>0</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2643,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>41800</v>
+        <v>46900</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
@@ -2651,19 +2634,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="C65">
-        <v>55700</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>33300</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -2672,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>40700</v>
+        <v>45300</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
@@ -2680,16 +2663,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="C66">
-        <v>16500</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>23000</v>
+        <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>43200</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -2701,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>39500</v>
+        <v>43200</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
@@ -2709,7 +2692,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -2718,10 +2701,10 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>34500</v>
+        <v>43200</v>
       </c>
       <c r="F67">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -2730,7 +2713,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>37800</v>
+        <v>43200</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
@@ -2738,13 +2721,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="C68">
-        <v>51100</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>41800</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2759,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>36100</v>
+        <v>41800</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
@@ -2767,16 +2750,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>16500</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="E69">
-        <v>34800</v>
+        <v>0</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -2788,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>34800</v>
+        <v>39500</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
@@ -2796,16 +2779,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="C70">
-        <v>34500</v>
+        <v>0</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>68200</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -2817,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>34500</v>
+        <v>38200</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
@@ -2825,16 +2808,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="C71">
-        <v>34300</v>
+        <v>0</v>
       </c>
       <c r="D71">
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>34800</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -2846,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>34300</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
@@ -2854,10 +2837,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C72">
-        <v>37600</v>
+        <v>34500</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2866,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="F72">
-        <v>11200</v>
+        <v>0</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -2875,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>33800</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
@@ -2883,10 +2866,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>34300</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -2895,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="F73">
-        <v>33400</v>
+        <v>0</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -2904,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>33400</v>
+        <v>34300</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
@@ -2912,7 +2895,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2941,10 +2924,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>31600</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2953,7 +2936,7 @@
         <v>0</v>
       </c>
       <c r="F75">
-        <v>32100</v>
+        <v>0</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -2962,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>32100</v>
+        <v>31600</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
@@ -2970,13 +2953,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>31400</v>
       </c>
       <c r="D76">
-        <v>62000</v>
+        <v>0</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2991,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>32000</v>
+        <v>31400</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
@@ -2999,10 +2982,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C77">
-        <v>31600</v>
+        <v>27400</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -3020,7 +3003,7 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>31600</v>
+        <v>27400</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
@@ -3028,13 +3011,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C78">
-        <v>31400</v>
+        <v>12400</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>29400</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3049,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>31400</v>
+        <v>26800</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
@@ -3057,19 +3040,19 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>26400</v>
       </c>
       <c r="E79">
         <v>0</v>
       </c>
       <c r="F79">
-        <v>30800</v>
+        <v>0</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -3078,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>30800</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
@@ -3089,7 +3072,7 @@
         <v>39</v>
       </c>
       <c r="C80">
-        <v>27400</v>
+        <v>26200</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -3107,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>27400</v>
+        <v>26200</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
@@ -3115,10 +3098,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C81">
-        <v>27400</v>
+        <v>55700</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3136,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>27400</v>
+        <v>25700</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
@@ -3144,19 +3127,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="C82">
-        <v>12400</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>29400</v>
+        <v>0</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>25600</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -3165,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>26800</v>
+        <v>25600</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
@@ -3173,13 +3156,13 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="D83">
-        <v>26400</v>
+        <v>0</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3194,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>26400</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
@@ -3202,10 +3185,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C84">
-        <v>26200</v>
+        <v>25000</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -3223,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="I84">
-        <v>26200</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
@@ -3231,19 +3214,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
       <c r="F85">
-        <v>25600</v>
+        <v>0</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -3252,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>25600</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
@@ -3263,7 +3246,7 @@
         <v>43</v>
       </c>
       <c r="C86">
-        <v>25000</v>
+        <v>23000</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -3281,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>25000</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
@@ -3292,7 +3275,7 @@
         <v>44</v>
       </c>
       <c r="C87">
-        <v>25000</v>
+        <v>22800</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -3310,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>25000</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
@@ -3318,13 +3301,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>22600</v>
       </c>
       <c r="D88">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3339,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>25000</v>
+        <v>22600</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
@@ -3347,10 +3330,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C89">
-        <v>23000</v>
+        <v>51100</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -3368,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="I89">
-        <v>23000</v>
+        <v>21100</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
@@ -3376,10 +3359,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C90">
-        <v>22800</v>
+        <v>35000</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -3397,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>22800</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
@@ -3405,16 +3388,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="C91">
-        <v>22600</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>18600</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -3426,7 +3409,7 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>22600</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
@@ -3434,10 +3417,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="C92">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -3446,7 +3429,7 @@
         <v>0</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>33400</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -3455,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>20000</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
@@ -3463,16 +3446,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>18100</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>18600</v>
+        <v>0</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -3484,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="I93">
-        <v>18600</v>
+        <v>18100</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
@@ -3492,10 +3475,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C94">
-        <v>18100</v>
+        <v>17700</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -3513,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>18100</v>
+        <v>17700</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
@@ -3521,13 +3504,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C95">
-        <v>17700</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>16900</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3542,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="I95">
-        <v>17700</v>
+        <v>16900</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
@@ -3550,19 +3533,19 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>16900</v>
+        <v>0</v>
       </c>
       <c r="E96">
         <v>0</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>30800</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -3571,7 +3554,7 @@
         <v>0</v>
       </c>
       <c r="I96">
-        <v>16900</v>
+        <v>15800</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
@@ -3579,7 +3562,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -3608,7 +3591,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -3637,13 +3620,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>27400</v>
       </c>
       <c r="D99">
-        <v>11600</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3658,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>11600</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
@@ -3666,16 +3649,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="E100">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -3687,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>11000</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
@@ -3695,7 +3678,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -3704,10 +3687,10 @@
         <v>0</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="F101">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -3716,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>9600</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
@@ -3724,10 +3707,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="C102">
-        <v>9400</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3736,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -3745,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="I102">
-        <v>9400</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
@@ -3753,10 +3736,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="C103">
-        <v>7400</v>
+        <v>9400</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -3765,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="F103">
-        <v>13900</v>
+        <v>0</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -3774,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>6300</v>
+        <v>9400</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
@@ -3782,10 +3765,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C104">
-        <v>3900</v>
+        <v>7400</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3794,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>13900</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -3803,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>3900</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
@@ -3811,13 +3794,13 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="D105">
-        <v>18900</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3840,13 +3823,13 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C106">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>18900</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3861,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="I106">
-        <v>2700</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.35">
@@ -3869,27 +3852,56 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="C107">
+        <v>2700</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>35</v>
+      </c>
+      <c r="C108">
         <v>30500</v>
       </c>
-      <c r="D107">
-        <v>0</v>
-      </c>
-      <c r="E107">
-        <v>0</v>
-      </c>
-      <c r="F107">
-        <v>0</v>
-      </c>
-      <c r="G107">
-        <v>0</v>
-      </c>
-      <c r="H107">
-        <v>0</v>
-      </c>
-      <c r="I107">
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
         <v>500</v>
       </c>
     </row>
